--- a/project/excel/modos_schema.xlsx
+++ b/project/excel/modos_schema.xlsx
@@ -16,8 +16,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReferenceSequence" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AlignmentSet" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VariantSet" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Array" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MODOCollection" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MassSpectrometryResults" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Array" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MODOCollection" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,7 +498,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF"</formula1>
+      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF,mzTab"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -510,6 +511,62 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>data_path</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>data_format</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_sample</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>has_reference</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF,mzTab"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -582,7 +639,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -603,15 +660,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>has_sample_processing</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -737,7 +799,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF"</formula1>
+      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF,mzTab"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -895,7 +957,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF"</formula1>
+      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF,mzTab"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -951,7 +1013,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF"</formula1>
+      <formula1>"CRAM,FASTQ,Zarr,FASTA,VCF,BCF,mzTab"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/project/excel/modos_schema.xlsx
+++ b/project/excel/modos_schema.xlsx
@@ -660,7 +660,7 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>has_sample_processing</t>
+          <t>sample_processing</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">

--- a/project/excel/modos_schema.xlsx
+++ b/project/excel/modos_schema.xlsx
@@ -649,49 +649,44 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>has_sample</t>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>has_data</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>has_data</t>
+          <t>omics_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>omics_type</t>
+          <t>sample_processing</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>sample_processing</t>
+          <t>id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>name</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"GENOMICS,TRANSCRIPTOMICS,METABOLOMICS,PROTEOMICS"</formula1>
     </dataValidation>
   </dataValidations>
